--- a/Database/db tests.xlsx
+++ b/Database/db tests.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="756">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -3430,6 +3430,255 @@
     <t xml:space="preserve">1. Go to PHPMyAdmin
 2. CALL update_product_by_id(1, 'test_name_de',  'test_description_en', 1000, 5, 50,10, 'test_description_preview_en', 'test_name_hu', 'test_name_en', 'test_description_hu','test_description_de','test_description_preview_hu', 'test_description_preview_de','test_category','test_manufacturer','test_brand', 'test_sku','test_active_ingredients','test_packaging','test_name','test_thumbnail_url', ‘0’);</t>
   </si>
+  <si>
+    <t xml:space="preserve">SP152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if delete_confirmations_by_user_id works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Go to PHPMyAdmin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">2. Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">delete_confirmations_by_user_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">(‘2’)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">It deletes the row with the matching user_id from the confirmations table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-2, SP-7, SP-17, SP-34, SP-37, SP-39, SP-40, SP-44, SP-50, SP-51, SP-52, SP-57, SP-86, SP-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if delete_post_comment_by_post_id works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Go to PHPMyAdmin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">2. Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">delete_post_comment_by_post_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">(‘1’)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Deletes every row from the post_comments table where post_id matches given id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP112, SP113, SP114, SP140, SP141, SP142, SP143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if get_confirmations_by_user_id works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Go to PHPMyAdmin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. Call get_confirmations_by_user_id  (‘28’)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Returns the rows from the confirmations table where user id matches given id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-2, SP-7, SP-17, SP-34, SP-37, SP-39, SP-40, SP-44, SP-51, SP-52, SP-57, SP-87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if get_product_status_by_id works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Go to PHPMyAdmin
+2. Call </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve">get_product_status_by_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (‘1’)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Returns the status of the row with the given id </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-8, SP-15, SP-22, SP-28, SP-42, SP-62, SP-69, SP-84, SP-85, SP-93, SP-106, SP128, SP129, SP151, SP157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if update_order_status_by_id works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Go to PHPMyAdmin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. Call  update_order_status_by_id (‘1’, ‘cancelled’)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Updates the status of the row with the given id in the orders table, with the inputted status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updates the status of the row with the given id in the orders table, with the inputted data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-11, SP-12, SP-18, SP-31, SP-49, SP-53, SP-59, SP118, SP121, SP122, SP126, SP147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test if update_product_status_by_id works</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. Go to PHPMyAdmin
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. Call update_product_status_by_id (‘1’, ‘1’)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Updates the status of the row with the given id in the products table, with the inputted status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP-8, SP-15, SP-22, SP-28, SP-42, SP-62, SP-69, SP-84, SP-85, SP-93, SP-106, SP128, SP129, SP151, SP155</t>
+  </si>
 </sst>
 </file>
 
@@ -3439,7 +3688,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3495,6 +3744,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -3609,7 +3870,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3684,6 +3945,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7284,7 +7553,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="23.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="13" t="n">
         <v>115</v>
       </c>
@@ -7311,7 +7580,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="13" t="n">
         <v>116</v>
       </c>
@@ -7340,7 +7609,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="13" t="n">
         <v>117</v>
       </c>
@@ -7369,7 +7638,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="88.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="13" t="n">
         <v>118</v>
       </c>
@@ -7398,7 +7667,7 @@
         <v>46104</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="66.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="13" t="n">
         <v>119</v>
       </c>
@@ -7482,7 +7751,7 @@
       <c r="CT120" s="18"/>
       <c r="CU120" s="18"/>
     </row>
-    <row r="121" customFormat="false" ht="33.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="13" t="n">
         <v>120</v>
       </c>
@@ -7566,7 +7835,7 @@
       <c r="CT121" s="18"/>
       <c r="CU121" s="18"/>
     </row>
-    <row r="122" customFormat="false" ht="88.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="13" t="n">
         <v>121</v>
       </c>
@@ -7650,7 +7919,7 @@
       <c r="CT122" s="18"/>
       <c r="CU122" s="18"/>
     </row>
-    <row r="123" customFormat="false" ht="55.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="13" t="n">
         <v>122</v>
       </c>
@@ -7734,7 +8003,7 @@
       <c r="CT123" s="18"/>
       <c r="CU123" s="18"/>
     </row>
-    <row r="124" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="13" t="n">
         <v>123</v>
       </c>
@@ -7853,7 +8122,7 @@
       <c r="CT124" s="18"/>
       <c r="CU124" s="18"/>
     </row>
-    <row r="125" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="13" t="n">
         <v>124</v>
       </c>
@@ -7937,7 +8206,7 @@
       <c r="CT125" s="18"/>
       <c r="CU125" s="18"/>
     </row>
-    <row r="126" customFormat="false" ht="77.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="13" t="n">
         <v>125</v>
       </c>
@@ -8021,7 +8290,7 @@
       <c r="CT126" s="18"/>
       <c r="CU126" s="18"/>
     </row>
-    <row r="127" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="13" t="n">
         <v>126</v>
       </c>
@@ -8105,7 +8374,7 @@
       <c r="CT127" s="18"/>
       <c r="CU127" s="18"/>
     </row>
-    <row r="128" customFormat="false" ht="109.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="13" t="n">
         <v>127</v>
       </c>
@@ -8189,7 +8458,7 @@
       <c r="CT128" s="18"/>
       <c r="CU128" s="18"/>
     </row>
-    <row r="129" customFormat="false" ht="66.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="13" t="n">
         <v>128</v>
       </c>
@@ -8357,7 +8626,7 @@
       <c r="CT130" s="18"/>
       <c r="CU130" s="18"/>
     </row>
-    <row r="131" customFormat="false" ht="77.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="13" t="n">
         <v>130</v>
       </c>
@@ -8441,7 +8710,7 @@
       <c r="CT131" s="18"/>
       <c r="CU131" s="18"/>
     </row>
-    <row r="132" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="13" t="n">
         <v>131</v>
       </c>
@@ -8525,7 +8794,7 @@
       <c r="CT132" s="18"/>
       <c r="CU132" s="18"/>
     </row>
-    <row r="133" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="13" t="n">
         <v>132</v>
       </c>
@@ -8609,7 +8878,7 @@
       <c r="CT133" s="18"/>
       <c r="CU133" s="18"/>
     </row>
-    <row r="134" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="13" t="n">
         <v>133</v>
       </c>
@@ -8693,7 +8962,7 @@
       <c r="CT134" s="18"/>
       <c r="CU134" s="18"/>
     </row>
-    <row r="135" customFormat="false" ht="33.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="13" t="n">
         <v>134</v>
       </c>
@@ -8777,7 +9046,7 @@
       <c r="CT135" s="18"/>
       <c r="CU135" s="18"/>
     </row>
-    <row r="136" customFormat="false" ht="33.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="13" t="n">
         <v>135</v>
       </c>
@@ -8861,7 +9130,7 @@
       <c r="CT136" s="18"/>
       <c r="CU136" s="18"/>
     </row>
-    <row r="137" customFormat="false" ht="33.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="13" t="n">
         <v>136</v>
       </c>
@@ -8945,7 +9214,7 @@
       <c r="CT137" s="18"/>
       <c r="CU137" s="18"/>
     </row>
-    <row r="138" customFormat="false" ht="66.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="13" t="n">
         <v>137</v>
       </c>
@@ -9029,7 +9298,7 @@
       <c r="CT138" s="18"/>
       <c r="CU138" s="18"/>
     </row>
-    <row r="139" customFormat="false" ht="33.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="13" t="n">
         <v>138</v>
       </c>
@@ -9197,7 +9466,7 @@
       <c r="CT140" s="18"/>
       <c r="CU140" s="18"/>
     </row>
-    <row r="141" customFormat="false" ht="88.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="13" t="n">
         <v>140</v>
       </c>
@@ -9281,7 +9550,7 @@
       <c r="CT141" s="18"/>
       <c r="CU141" s="18"/>
     </row>
-    <row r="142" customFormat="false" ht="55.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="13" t="n">
         <v>141</v>
       </c>
@@ -9365,7 +9634,7 @@
       <c r="CT142" s="18"/>
       <c r="CU142" s="18"/>
     </row>
-    <row r="143" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="13" t="n">
         <v>142</v>
       </c>
@@ -9449,7 +9718,7 @@
       <c r="CT143" s="18"/>
       <c r="CU143" s="18"/>
     </row>
-    <row r="144" customFormat="false" ht="66.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="13" t="n">
         <v>143</v>
       </c>
@@ -9533,7 +9802,7 @@
       <c r="CT144" s="18"/>
       <c r="CU144" s="18"/>
     </row>
-    <row r="145" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="13" t="n">
         <v>144</v>
       </c>
@@ -10118,7 +10387,7 @@
       <c r="CT151" s="18"/>
       <c r="CU151" s="18"/>
     </row>
-    <row r="152" customFormat="false" ht="66.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="13" t="n">
         <v>151</v>
       </c>
@@ -10142,6 +10411,9 @@
       </c>
       <c r="H152" s="7" t="s">
         <v>417</v>
+      </c>
+      <c r="I152" s="19" t="n">
+        <v>46139</v>
       </c>
       <c r="AS152" s="18"/>
       <c r="AT152" s="18"/>
@@ -10199,7 +10471,34 @@
       <c r="CT152" s="18"/>
       <c r="CU152" s="18"/>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="13" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="13" t="s">
+        <v>725</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="D153" s="17" t="s">
+        <v>727</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="I153" s="19" t="n">
+        <v>46139</v>
+      </c>
       <c r="AS153" s="18"/>
       <c r="AT153" s="18"/>
       <c r="AU153" s="18"/>
@@ -10256,7 +10555,34 @@
       <c r="CT153" s="18"/>
       <c r="CU153" s="18"/>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="48.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="13" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>730</v>
+      </c>
+      <c r="C154" s="20" t="s">
+        <v>731</v>
+      </c>
+      <c r="D154" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I154" s="19" t="n">
+        <v>46139</v>
+      </c>
       <c r="AS154" s="18"/>
       <c r="AT154" s="18"/>
       <c r="AU154" s="18"/>
@@ -10313,7 +10639,34 @@
       <c r="CT154" s="18"/>
       <c r="CU154" s="18"/>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="67.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="13" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>735</v>
+      </c>
+      <c r="C155" s="20" t="s">
+        <v>736</v>
+      </c>
+      <c r="D155" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="I155" s="19" t="n">
+        <v>46139</v>
+      </c>
       <c r="AS155" s="18"/>
       <c r="AT155" s="18"/>
       <c r="AU155" s="18"/>
@@ -10370,7 +10723,34 @@
       <c r="CT155" s="18"/>
       <c r="CU155" s="18"/>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="54.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="13" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>740</v>
+      </c>
+      <c r="C156" s="20" t="s">
+        <v>741</v>
+      </c>
+      <c r="D156" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="I156" s="19" t="n">
+        <v>46139</v>
+      </c>
       <c r="AS156" s="18"/>
       <c r="AT156" s="18"/>
       <c r="AU156" s="18"/>
@@ -10427,7 +10807,34 @@
       <c r="CT156" s="18"/>
       <c r="CU156" s="18"/>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="43.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A157" s="13" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="13" t="s">
+        <v>745</v>
+      </c>
+      <c r="C157" s="20" t="s">
+        <v>746</v>
+      </c>
+      <c r="D157" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="I157" s="19" t="n">
+        <v>46139</v>
+      </c>
       <c r="AS157" s="18"/>
       <c r="AT157" s="18"/>
       <c r="AU157" s="18"/>
@@ -10484,7 +10891,34 @@
       <c r="CT157" s="18"/>
       <c r="CU157" s="18"/>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="71.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="13" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="C158" s="20" t="s">
+        <v>752</v>
+      </c>
+      <c r="D158" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="I158" s="19" t="n">
+        <v>46139</v>
+      </c>
       <c r="AS158" s="18"/>
       <c r="AT158" s="18"/>
       <c r="AU158" s="18"/>
